--- a/02_Basic_Excel_for_Data_Analytics/16P_Images-and-Shapes.xlsx
+++ b/02_Basic_Excel_for_Data_Analytics/16P_Images-and-Shapes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01 COURSES\Learn_Data_Analytics_by_CWH\02_Basic_Excel_for_Data_Analytics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA92B0B1-DDAE-4D8C-9E78-87D0CDA9E4E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD47B77-CD82-4F16-AB98-8EE2EADB4570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{07044EDC-F1DB-434C-8E80-40614FFD95E5}"/>
   </bookViews>
@@ -1416,8 +1416,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="731704" y="128"/>
-          <a:ext cx="504457" cy="504457"/>
+          <a:off x="727639" y="185"/>
+          <a:ext cx="508101" cy="508101"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -1483,8 +1483,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="805580" y="74004"/>
-        <a:ext cx="356705" cy="356705"/>
+        <a:off x="802049" y="74595"/>
+        <a:ext cx="359281" cy="359281"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{403F30DF-F383-4C9F-B3AE-3EE0E7FBFDA9}">
@@ -1494,8 +1494,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2160000">
-          <a:off x="1220384" y="387988"/>
-          <a:ext cx="134793" cy="170254"/>
+          <a:off x="1219715" y="390547"/>
+          <a:ext cx="135209" cy="171484"/>
         </a:xfrm>
         <a:prstGeom prst="rightArrow">
           <a:avLst>
@@ -1552,8 +1552,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1224245" y="410155"/>
-        <a:ext cx="94355" cy="102152"/>
+        <a:off x="1223588" y="412923"/>
+        <a:ext cx="94646" cy="102890"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{FE9F43E0-8F5C-4E3E-B452-D6C15DD2DD05}">
@@ -1563,8 +1563,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="1345574" y="446130"/>
-          <a:ext cx="504457" cy="504457"/>
+          <a:off x="1345092" y="448791"/>
+          <a:ext cx="508101" cy="508101"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -1630,8 +1630,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1419450" y="520006"/>
-        <a:ext cx="356705" cy="356705"/>
+        <a:off x="1419502" y="523201"/>
+        <a:ext cx="359281" cy="359281"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{492902E4-0448-4B77-B634-5CFD960EC5C4}">
@@ -1641,8 +1641,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="6480000">
-          <a:off x="1414346" y="970427"/>
-          <a:ext cx="134793" cy="170254"/>
+          <a:off x="1414797" y="976390"/>
+          <a:ext cx="135209" cy="171484"/>
         </a:xfrm>
         <a:prstGeom prst="rightArrow">
           <a:avLst>
@@ -1699,8 +1699,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm rot="10800000">
-        <a:off x="1440813" y="985249"/>
-        <a:ext cx="94355" cy="102152"/>
+        <a:off x="1441346" y="991398"/>
+        <a:ext cx="94646" cy="102890"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{55A9A74E-778D-4F66-8A02-869B7DABFB23}">
@@ -1710,8 +1710,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="1111096" y="1167778"/>
-          <a:ext cx="504457" cy="504457"/>
+          <a:off x="1109246" y="1174651"/>
+          <a:ext cx="508101" cy="508101"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -1777,8 +1777,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1184972" y="1241654"/>
-        <a:ext cx="356705" cy="356705"/>
+        <a:off x="1183656" y="1249061"/>
+        <a:ext cx="359281" cy="359281"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6D9EC480-BF3D-4E6C-AA28-AA45A192F5AE}">
@@ -1788,8 +1788,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="10800000">
-          <a:off x="920351" y="1334879"/>
-          <a:ext cx="134793" cy="170254"/>
+          <a:off x="917911" y="1342959"/>
+          <a:ext cx="135209" cy="171484"/>
         </a:xfrm>
         <a:prstGeom prst="rightArrow">
           <a:avLst>
@@ -1846,8 +1846,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm rot="10800000">
-        <a:off x="960789" y="1368930"/>
-        <a:ext cx="94355" cy="102152"/>
+        <a:off x="958474" y="1377256"/>
+        <a:ext cx="94646" cy="102890"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{DCB034D5-66B4-4977-B86F-B77681E21EF3}">
@@ -1857,8 +1857,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="352311" y="1167778"/>
-          <a:ext cx="504457" cy="504457"/>
+          <a:off x="346032" y="1174651"/>
+          <a:ext cx="508101" cy="508101"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -1924,8 +1924,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="426187" y="1241654"/>
-        <a:ext cx="356705" cy="356705"/>
+        <a:off x="420442" y="1249061"/>
+        <a:ext cx="359281" cy="359281"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{47F35FA4-9599-4A53-9B6A-A1D771150084}">
@@ -1935,8 +1935,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="15120000">
-          <a:off x="421083" y="977684"/>
-          <a:ext cx="134793" cy="170254"/>
+          <a:off x="415737" y="983669"/>
+          <a:ext cx="135209" cy="171484"/>
         </a:xfrm>
         <a:prstGeom prst="rightArrow">
           <a:avLst>
@@ -1993,8 +1993,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm rot="10800000">
-        <a:off x="447550" y="1030964"/>
-        <a:ext cx="94355" cy="102152"/>
+        <a:off x="442286" y="1037255"/>
+        <a:ext cx="94646" cy="102890"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4455899D-D729-4EF6-831B-FDAA275810EC}">
@@ -2004,8 +2004,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="117834" y="446130"/>
-          <a:ext cx="504457" cy="504457"/>
+          <a:off x="110186" y="448791"/>
+          <a:ext cx="508101" cy="508101"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -2071,8 +2071,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="191710" y="520006"/>
-        <a:ext cx="356705" cy="356705"/>
+        <a:off x="184596" y="523201"/>
+        <a:ext cx="359281" cy="359281"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A6BD09A5-C78A-44D2-970B-BFA8FFD31B4A}">
@@ -2082,8 +2082,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19440000">
-          <a:off x="606514" y="392473"/>
-          <a:ext cx="134793" cy="170254"/>
+          <a:off x="602262" y="395046"/>
+          <a:ext cx="135209" cy="171484"/>
         </a:xfrm>
         <a:prstGeom prst="rightArrow">
           <a:avLst>
@@ -2140,8 +2140,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="610375" y="438408"/>
-        <a:ext cx="94355" cy="102152"/>
+        <a:off x="606135" y="441264"/>
+        <a:ext cx="94646" cy="102890"/>
       </dsp:txXfrm>
     </dsp:sp>
   </dsp:spTree>
@@ -3632,13 +3632,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>51257</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>181845</xdr:rowOff>
+      <xdr:rowOff>177466</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>346220</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>254001</xdr:rowOff>
+      <xdr:rowOff>249622</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3679,8 +3679,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="661215" y="181845"/>
-          <a:ext cx="294963" cy="256395"/>
+          <a:off x="659981" y="177466"/>
+          <a:ext cx="294963" cy="256087"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
